--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573440584</v>
+        <v>46157.93114284285</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114284285</v>
+        <v>46157.93180960686</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93180960686</v>
+        <v>46157.93404836891</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93404836891</v>
+        <v>46157.93722905311</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93722905311</v>
+        <v>46158.28220774669</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28220774669</v>
+        <v>46158.29697767862</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29697767862</v>
+        <v>46158.29820354176</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820354176</v>
+        <v>46158.33391743678</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391743678</v>
+        <v>46158.36861567119</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861567119</v>
+        <v>46158.37292195118</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
